--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw By Marriage.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw By Marriage.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw By Marriage.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw By Marriage.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>Choctaw</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -438,14 +444,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1673"/>
+  <dimension ref="A1:Q1673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="34.85546875" customWidth="1"/>
     <col min="14" max="14" width="56.42578125" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,8 +499,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -509,7 +523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -529,7 +543,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -549,7 +563,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -569,7 +583,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -589,7 +603,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -609,7 +623,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -629,7 +643,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -649,7 +663,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -669,7 +683,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -689,7 +703,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -709,7 +723,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -729,7 +743,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -749,7 +763,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -769,7 +783,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -29024,8 +29038,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1406" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1406" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1406">
+        <v>-1</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1406" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1406" t="s">
+        <v>28</v>
+      </c>
       <c r="L1406" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1406" t="s">
+        <v>28</v>
       </c>
       <c r="N1406" t="str">
         <f t="shared" si="71"/>
@@ -29044,8 +29085,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1407" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1407" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1407">
+        <v>-1</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1407" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1407" t="s">
+        <v>28</v>
+      </c>
       <c r="L1407" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1407" t="s">
+        <v>28</v>
       </c>
       <c r="N1407" t="str">
         <f t="shared" si="71"/>
@@ -29064,8 +29132,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1408" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1408" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1408">
+        <v>-1</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1408" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1408" t="s">
+        <v>28</v>
+      </c>
       <c r="L1408" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1408" t="s">
+        <v>28</v>
       </c>
       <c r="N1408" t="str">
         <f t="shared" si="71"/>
@@ -29084,8 +29179,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1409" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1409" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1409">
+        <v>-1</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1409" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1409" t="s">
+        <v>28</v>
+      </c>
       <c r="L1409" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1409" t="s">
+        <v>28</v>
       </c>
       <c r="N1409" t="str">
         <f t="shared" si="71"/>
@@ -29104,8 +29226,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1410" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1410" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1410">
+        <v>-1</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1410" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1410" t="s">
+        <v>28</v>
+      </c>
       <c r="L1410" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1410" t="s">
+        <v>28</v>
       </c>
       <c r="N1410" t="str">
         <f t="shared" si="71"/>
@@ -29124,8 +29273,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1411" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1411">
+        <v>-1</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1411" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1411" t="s">
+        <v>28</v>
+      </c>
       <c r="L1411" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1411" t="s">
+        <v>28</v>
       </c>
       <c r="N1411" t="str">
         <f t="shared" si="71"/>
@@ -29164,8 +29340,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1413" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1413" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1413" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1413">
+        <v>-1</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1413" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1413" t="s">
+        <v>28</v>
+      </c>
       <c r="L1413" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1413" t="s">
+        <v>28</v>
       </c>
       <c r="N1413" t="str">
         <f t="shared" si="71"/>
@@ -29204,8 +29407,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1415" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1415" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1415" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1415">
+        <v>-1</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1415" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1415" t="s">
+        <v>28</v>
+      </c>
       <c r="L1415" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1415" t="s">
+        <v>28</v>
       </c>
       <c r="N1415" t="str">
         <f t="shared" si="71"/>
@@ -29244,8 +29474,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1417" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1417" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1417">
+        <v>-1</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1417" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1417" t="s">
+        <v>28</v>
+      </c>
       <c r="L1417" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1417" t="s">
+        <v>28</v>
       </c>
       <c r="N1417" t="str">
         <f t="shared" si="71"/>
@@ -29344,8 +29601,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1422" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1422" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1422">
+        <v>-1</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1422" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1422" t="s">
+        <v>28</v>
+      </c>
       <c r="L1422" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1422" t="s">
+        <v>28</v>
       </c>
       <c r="N1422" t="str">
         <f t="shared" si="71"/>
@@ -29384,8 +29668,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1424" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1424" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1424">
+        <v>-1</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1424" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1424" t="s">
+        <v>28</v>
+      </c>
       <c r="L1424" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1424" t="s">
+        <v>28</v>
       </c>
       <c r="N1424" t="str">
         <f t="shared" si="71"/>
@@ -29484,8 +29795,35 @@
         <f t="shared" si="70"/>
         <v>122</v>
       </c>
+      <c r="D1429" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1429">
+        <v>-1</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1429" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1429" t="s">
+        <v>28</v>
+      </c>
       <c r="L1429" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1429" t="s">
+        <v>28</v>
       </c>
       <c r="N1429" t="str">
         <f t="shared" si="71"/>
@@ -30204,8 +30542,35 @@
         <f t="shared" si="73"/>
         <v>122</v>
       </c>
+      <c r="D1465" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1465" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1465">
+        <v>-1</v>
+      </c>
+      <c r="I1465" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1465" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1465" t="s">
+        <v>28</v>
+      </c>
       <c r="L1465" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1465" t="s">
+        <v>28</v>
       </c>
       <c r="N1465" t="str">
         <f t="shared" si="74"/>
@@ -33705,35 +34070,8 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
-      <c r="D1601" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1601" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1601" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1601" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1601">
-        <v>-1</v>
-      </c>
-      <c r="I1601" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1601" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1601" t="s">
-        <v>28</v>
-      </c>
       <c r="L1601" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1601" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1601" t="str">
         <f t="shared" si="82"/>
@@ -33752,8 +34090,35 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
+      <c r="D1602" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1602" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1602" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1602" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1602">
+        <v>-1</v>
+      </c>
+      <c r="I1602" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1602" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1602" t="s">
+        <v>28</v>
+      </c>
       <c r="L1602" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1602" t="s">
+        <v>28</v>
       </c>
       <c r="N1602" t="str">
         <f t="shared" si="82"/>
@@ -33892,35 +34257,8 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
-      <c r="D1609" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1609" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1609" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1609" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1609">
-        <v>-1</v>
-      </c>
-      <c r="I1609" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1609" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1609" t="s">
-        <v>28</v>
-      </c>
       <c r="L1609" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1609" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1609" t="str">
         <f t="shared" si="82"/>
@@ -33939,8 +34277,35 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
+      <c r="D1610" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1610">
+        <v>-1</v>
+      </c>
+      <c r="I1610" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1610" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1610" t="s">
+        <v>28</v>
+      </c>
       <c r="L1610" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1610" t="s">
+        <v>28</v>
       </c>
       <c r="N1610" t="str">
         <f t="shared" si="82"/>
@@ -34019,35 +34384,8 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
-      <c r="D1614" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1614" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1614" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1614" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1614">
-        <v>-1</v>
-      </c>
-      <c r="I1614" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1614" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1614" t="s">
-        <v>28</v>
-      </c>
       <c r="L1614" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1614" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1614" t="str">
         <f t="shared" si="82"/>
@@ -34066,8 +34404,35 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
+      <c r="D1615" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1615" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1615" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1615">
+        <v>-1</v>
+      </c>
+      <c r="I1615" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1615" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1615" t="s">
+        <v>28</v>
+      </c>
       <c r="L1615" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1615" t="s">
+        <v>28</v>
       </c>
       <c r="N1615" t="str">
         <f t="shared" si="82"/>
@@ -34226,35 +34591,8 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
-      <c r="D1623" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1623" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1623" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1623" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1623">
-        <v>-1</v>
-      </c>
-      <c r="I1623" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1623" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1623" t="s">
-        <v>28</v>
-      </c>
       <c r="L1623" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1623" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1623" t="str">
         <f t="shared" si="82"/>
@@ -34414,8 +34752,35 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
+      <c r="D1627" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1627">
+        <v>-1</v>
+      </c>
+      <c r="I1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1627" t="s">
+        <v>28</v>
+      </c>
       <c r="L1627" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1627" t="s">
+        <v>28</v>
       </c>
       <c r="N1627" t="str">
         <f t="shared" si="82"/>
@@ -34434,35 +34799,8 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
-      <c r="D1628" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1628" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1628" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1628" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1628">
-        <v>-1</v>
-      </c>
-      <c r="I1628" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1628" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1628" t="s">
-        <v>28</v>
-      </c>
       <c r="L1628" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1628" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1628" t="str">
         <f t="shared" si="82"/>
@@ -34481,8 +34819,35 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
+      <c r="D1629" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1629">
+        <v>-1</v>
+      </c>
+      <c r="I1629" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1629" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1629" t="s">
+        <v>28</v>
+      </c>
       <c r="L1629" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1629" t="s">
+        <v>28</v>
       </c>
       <c r="N1629" t="str">
         <f t="shared" si="82"/>
@@ -34581,35 +34946,8 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
-      <c r="D1634" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1634" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1634" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1634" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1634">
-        <v>-1</v>
-      </c>
-      <c r="I1634" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1634" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1634" t="s">
-        <v>28</v>
-      </c>
       <c r="L1634" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1634" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1634" t="str">
         <f t="shared" si="82"/>
@@ -34628,8 +34966,35 @@
         <f t="shared" si="81"/>
         <v>123</v>
       </c>
+      <c r="D1635" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1635">
+        <v>-1</v>
+      </c>
+      <c r="I1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1635" t="s">
+        <v>28</v>
+      </c>
       <c r="L1635" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1635" t="s">
+        <v>28</v>
       </c>
       <c r="N1635" t="str">
         <f t="shared" si="82"/>
@@ -34666,35 +35031,8 @@
         <f>C1636</f>
         <v>124</v>
       </c>
-      <c r="D1637" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1637" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1637" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1637" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1637">
-        <v>-1</v>
-      </c>
-      <c r="I1637" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1637" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1637" t="s">
-        <v>28</v>
-      </c>
       <c r="L1637" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1637" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N1637" t="str">
         <f>N1636</f>
@@ -35418,8 +35756,35 @@
         <f t="shared" si="84"/>
         <v>124</v>
       </c>
+      <c r="D1653" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1653" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1653" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1653" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1653">
+        <v>-1</v>
+      </c>
+      <c r="I1653" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1653" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1653" t="s">
+        <v>28</v>
+      </c>
       <c r="L1653" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="M1653" t="s">
+        <v>28</v>
       </c>
       <c r="N1653" t="str">
         <f t="shared" si="85"/>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw By Marriage.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw By Marriage.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -109,10 +109,13 @@
     <t>Choctaw</t>
   </si>
   <si>
-    <t>Image Name</t>
+    <t>TribeRelationship</t>
   </si>
   <si>
-    <t>Image Binary</t>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>ImageName</t>
   </si>
 </sst>
 </file>
@@ -444,16 +447,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q1673"/>
+  <dimension ref="A1:R1673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="34.85546875" customWidth="1"/>
     <col min="14" max="14" width="56.42578125" customWidth="1"/>
     <col min="16" max="16" width="13.5703125" customWidth="1"/>
     <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -500,13 +504,16 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -523,7 +530,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -543,7 +550,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -563,7 +570,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -583,7 +590,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -603,7 +610,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -623,7 +630,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -643,7 +650,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -663,7 +670,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -683,7 +690,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -703,7 +710,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -723,7 +730,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -743,7 +750,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -763,7 +770,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -783,7 +790,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 114</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
